--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -1198,7 +1198,7 @@
     <t>0.4421,0.6062,0.0350,0.0044</t>
   </si>
   <si>
-    <t>0.3611,0.6768,0.0383,0.0045</t>
+    <t>0.3610,0.6768,0.0383,0.0045</t>
   </si>
   <si>
     <t>0.9507,0.0268,0.0142,0.0057</t>
@@ -1240,7 +1240,7 @@
     <t>0.8098,0.0087,0.2018,0.0019</t>
   </si>
   <si>
-    <t>0.5985,0.1157,0.2394,0.0128</t>
+    <t>0.5985,0.1158,0.2394,0.0128</t>
   </si>
   <si>
     <t>0.4556,0.0077,0.4366,0.0220</t>
@@ -1306,7 +1306,7 @@
     <t>0.4023,0.4504,0.1482,0.0411</t>
   </si>
   <si>
-    <t>0.7860,0.0692,0.1299,0.0058</t>
+    <t>0.7860,0.0693,0.1299,0.0058</t>
   </si>
   <si>
     <t>0.6686,0.0494,0.1894,0.0390</t>
@@ -1360,7 +1360,7 @@
     <t>0.8938,0.0764,0.0298,0.0022</t>
   </si>
   <si>
-    <t>0.3664,0.3522,0.1980,0.0090</t>
+    <t>0.3663,0.3522,0.1980,0.0090</t>
   </si>
   <si>
     <t>0.8207,0.1621,0.0285,0.0020</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -808,37 +808,43 @@
     <t>[[0.0, 1.0, 1.0, 0.0]]</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,1</t>
+  </si>
+  <si>
     <t>1,0,0,0</t>
   </si>
   <si>
-    <t>0,0,0,1</t>
-  </si>
-  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.4960,0.0125,0.0779,0.2913</t>
-  </si>
-  <si>
-    <t>0.2385,0.0210,0.0121,0.7706</t>
-  </si>
-  <si>
-    <t>0.6428,0.0104,0.0237,0.2202</t>
-  </si>
-  <si>
-    <t>0.6829,0.0248,0.0198,0.1525</t>
+    <t>0.4962,0.0125,0.0778,0.2911</t>
+  </si>
+  <si>
+    <t>0.2386,0.0210,0.0121,0.7704</t>
+  </si>
+  <si>
+    <t>0.6431,0.0104,0.0237,0.2199</t>
+  </si>
+  <si>
+    <t>0.6831,0.0248,0.0198,0.1524</t>
   </si>
   <si>
     <t>0.9664,0.0429,0.0072,0.0010</t>
   </si>
   <si>
-    <t>0.9521,0.0601,0.0079,0.0011</t>
+    <t>0.9522,0.0601,0.0079,0.0011</t>
   </si>
   <si>
     <t>0.9548,0.0481,0.0093,0.0007</t>
@@ -847,7 +853,7 @@
     <t>0.9617,0.0370,0.0084,0.0008</t>
   </si>
   <si>
-    <t>0.9211,0.0414,0.0096,0.0148</t>
+    <t>0.9212,0.0414,0.0096,0.0148</t>
   </si>
   <si>
     <t>0.9439,0.0748,0.0100,0.0016</t>
@@ -859,19 +865,19 @@
     <t>0.9607,0.0491,0.0079,0.0009</t>
   </si>
   <si>
-    <t>0.5856,0.0432,0.3625,0.0148</t>
-  </si>
-  <si>
-    <t>0.4194,0.0703,0.5163,0.0146</t>
-  </si>
-  <si>
-    <t>0.5882,0.0070,0.4962,0.0020</t>
-  </si>
-  <si>
-    <t>0.3371,0.0275,0.6616,0.0141</t>
-  </si>
-  <si>
-    <t>0.8683,0.0078,0.1363,0.0009</t>
+    <t>0.5859,0.0432,0.3622,0.0148</t>
+  </si>
+  <si>
+    <t>0.4196,0.0703,0.5161,0.0146</t>
+  </si>
+  <si>
+    <t>0.5884,0.0070,0.4959,0.0020</t>
+  </si>
+  <si>
+    <t>0.3373,0.0275,0.6615,0.0141</t>
+  </si>
+  <si>
+    <t>0.8683,0.0078,0.1362,0.0009</t>
   </si>
   <si>
     <t>0.0142,0.9757,0.0408,0.0029</t>
@@ -880,55 +886,55 @@
     <t>0.0559,0.9427,0.0288,0.0023</t>
   </si>
   <si>
-    <t>0.1066,0.6651,0.1603,0.1894</t>
-  </si>
-  <si>
-    <t>0.1460,0.8748,0.0261,0.0022</t>
+    <t>0.1066,0.6651,0.1603,0.1893</t>
+  </si>
+  <si>
+    <t>0.1461,0.8748,0.0261,0.0022</t>
   </si>
   <si>
     <t>0.0066,0.9843,0.1041,0.0020</t>
   </si>
   <si>
-    <t>0.5147,0.0088,0.5425,0.0050</t>
-  </si>
-  <si>
-    <t>0.3399,0.0202,0.6859,0.0101</t>
-  </si>
-  <si>
-    <t>0.3604,0.0033,0.7473,0.0012</t>
-  </si>
-  <si>
-    <t>0.2816,0.0163,0.7403,0.0096</t>
-  </si>
-  <si>
-    <t>0.3025,0.0101,0.7525,0.0043</t>
-  </si>
-  <si>
-    <t>0.3056,0.0033,0.7711,0.0019</t>
-  </si>
-  <si>
-    <t>0.1737,0.0026,0.8624,0.0026</t>
-  </si>
-  <si>
-    <t>0.5611,0.2867,0.1211,0.0084</t>
-  </si>
-  <si>
-    <t>0.6433,0.1846,0.1135,0.0734</t>
-  </si>
-  <si>
-    <t>0.4033,0.0319,0.5393,0.0083</t>
-  </si>
-  <si>
-    <t>0.1659,0.6259,0.2836,0.0207</t>
-  </si>
-  <si>
-    <t>0.8814,0.0771,0.0379,0.0045</t>
-  </si>
-  <si>
-    <t>0.8971,0.0417,0.0533,0.0015</t>
-  </si>
-  <si>
-    <t>0.5310,0.4836,0.0671,0.0121</t>
+    <t>0.5148,0.0088,0.5424,0.0050</t>
+  </si>
+  <si>
+    <t>0.3401,0.0202,0.6857,0.0101</t>
+  </si>
+  <si>
+    <t>0.3605,0.0033,0.7473,0.0012</t>
+  </si>
+  <si>
+    <t>0.2817,0.0163,0.7403,0.0096</t>
+  </si>
+  <si>
+    <t>0.3027,0.0101,0.7524,0.0043</t>
+  </si>
+  <si>
+    <t>0.3057,0.0033,0.7711,0.0019</t>
+  </si>
+  <si>
+    <t>0.1738,0.0026,0.8623,0.0026</t>
+  </si>
+  <si>
+    <t>0.5613,0.2867,0.1210,0.0084</t>
+  </si>
+  <si>
+    <t>0.6435,0.1846,0.1134,0.0734</t>
+  </si>
+  <si>
+    <t>0.4036,0.0319,0.5390,0.0082</t>
+  </si>
+  <si>
+    <t>0.1659,0.6260,0.2836,0.0207</t>
+  </si>
+  <si>
+    <t>0.8814,0.0771,0.0378,0.0045</t>
+  </si>
+  <si>
+    <t>0.8972,0.0417,0.0532,0.0015</t>
+  </si>
+  <si>
+    <t>0.5311,0.4835,0.0671,0.0121</t>
   </si>
   <si>
     <t>0.0562,0.9171,0.0896,0.0108</t>
@@ -937,16 +943,16 @@
     <t>0.0133,0.8888,0.5065,0.0096</t>
   </si>
   <si>
-    <t>0.0201,0.0752,0.9429,0.0069</t>
+    <t>0.0201,0.0753,0.9429,0.0069</t>
   </si>
   <si>
     <t>0.1189,0.0233,0.8899,0.0065</t>
   </si>
   <si>
-    <t>0.2388,0.0058,0.6440,0.0257</t>
-  </si>
-  <si>
-    <t>0.0351,0.4548,0.7363,0.0131</t>
+    <t>0.2390,0.0058,0.6439,0.0256</t>
+  </si>
+  <si>
+    <t>0.0351,0.4549,0.7363,0.0130</t>
   </si>
   <si>
     <t>0.0044,0.9656,0.1583,0.0152</t>
@@ -955,7 +961,7 @@
     <t>0.0825,0.0581,0.8751,0.0147</t>
   </si>
   <si>
-    <t>0.1953,0.1399,0.0457,0.6757</t>
+    <t>0.1954,0.1399,0.0457,0.6754</t>
   </si>
   <si>
     <t>0.0009,0.9955,0.0192,0.0017</t>
@@ -976,13 +982,13 @@
     <t>0.1666,0.0054,0.8661,0.0038</t>
   </si>
   <si>
-    <t>0.4072,0.0027,0.7133,0.0007</t>
+    <t>0.4073,0.0027,0.7132,0.0007</t>
   </si>
   <si>
     <t>0.2167,0.0041,0.8452,0.0016</t>
   </si>
   <si>
-    <t>0.2032,0.0136,0.8064,0.0082</t>
+    <t>0.2033,0.0136,0.8063,0.0082</t>
   </si>
   <si>
     <t>0.9170,0.0866,0.0155,0.0011</t>
@@ -991,13 +997,13 @@
     <t>0.9526,0.0387,0.0124,0.0007</t>
   </si>
   <si>
-    <t>0.9464,0.0529,0.0135,0.0025</t>
-  </si>
-  <si>
-    <t>0.8496,0.0559,0.0645,0.0029</t>
-  </si>
-  <si>
-    <t>0.9567,0.0338,0.0119,0.0006</t>
+    <t>0.9464,0.0529,0.0134,0.0024</t>
+  </si>
+  <si>
+    <t>0.8496,0.0559,0.0644,0.0029</t>
+  </si>
+  <si>
+    <t>0.9568,0.0338,0.0119,0.0006</t>
   </si>
   <si>
     <t>0.9630,0.0356,0.0096,0.0006</t>
@@ -1015,7 +1021,7 @@
     <t>0.0393,0.0156,0.9538,0.0047</t>
   </si>
   <si>
-    <t>0.0070,0.9184,0.7304,0.0031</t>
+    <t>0.0070,0.9184,0.7303,0.0031</t>
   </si>
   <si>
     <t>0.0061,0.0578,0.9664,0.0042</t>
@@ -1027,40 +1033,40 @@
     <t>0.0006,0.9962,0.0348,0.0008</t>
   </si>
   <si>
-    <t>0.8893,0.0162,0.0815,0.0025</t>
-  </si>
-  <si>
-    <t>0.5291,0.1402,0.2972,0.0548</t>
-  </si>
-  <si>
-    <t>0.3320,0.1048,0.4948,0.0279</t>
-  </si>
-  <si>
-    <t>0.0144,0.8356,0.6654,0.0118</t>
-  </si>
-  <si>
-    <t>0.0177,0.7714,0.8371,0.0043</t>
+    <t>0.8894,0.0162,0.0814,0.0025</t>
+  </si>
+  <si>
+    <t>0.5293,0.1402,0.2971,0.0548</t>
+  </si>
+  <si>
+    <t>0.3321,0.1048,0.4948,0.0279</t>
+  </si>
+  <si>
+    <t>0.0144,0.8357,0.6654,0.0118</t>
+  </si>
+  <si>
+    <t>0.0177,0.7716,0.8370,0.0043</t>
   </si>
   <si>
     <t>0.0007,0.9956,0.1439,0.0008</t>
   </si>
   <si>
-    <t>0.0062,0.9483,0.5045,0.0043</t>
-  </si>
-  <si>
-    <t>0.1045,0.0104,0.0221,0.9238</t>
-  </si>
-  <si>
-    <t>0.1252,0.0329,0.0134,0.9025</t>
-  </si>
-  <si>
-    <t>0.1922,0.0090,0.0071,0.8513</t>
-  </si>
-  <si>
-    <t>0.2752,0.0098,0.0103,0.7543</t>
-  </si>
-  <si>
-    <t>0.1630,0.0117,0.0155,0.8742</t>
+    <t>0.0062,0.9484,0.5045,0.0043</t>
+  </si>
+  <si>
+    <t>0.1046,0.0104,0.0221,0.9237</t>
+  </si>
+  <si>
+    <t>0.1253,0.0329,0.0134,0.9024</t>
+  </si>
+  <si>
+    <t>0.1923,0.0090,0.0071,0.8512</t>
+  </si>
+  <si>
+    <t>0.2755,0.0098,0.0103,0.7540</t>
+  </si>
+  <si>
+    <t>0.1632,0.0117,0.0155,0.8741</t>
   </si>
   <si>
     <t>0.0492,0.0341,0.0181,0.9729</t>
@@ -1069,28 +1075,28 @@
     <t>0.0044,0.9785,0.3461,0.0029</t>
   </si>
   <si>
-    <t>0.0177,0.3613,0.9333,0.0028</t>
-  </si>
-  <si>
-    <t>0.0582,0.3669,0.7570,0.0185</t>
-  </si>
-  <si>
-    <t>0.0319,0.3788,0.8832,0.0064</t>
+    <t>0.0177,0.3616,0.9333,0.0028</t>
+  </si>
+  <si>
+    <t>0.0582,0.3671,0.7570,0.0185</t>
+  </si>
+  <si>
+    <t>0.0319,0.3791,0.8831,0.0064</t>
   </si>
   <si>
     <t>0.0052,0.9668,0.5424,0.0024</t>
   </si>
   <si>
-    <t>0.0184,0.8947,0.4700,0.0087</t>
+    <t>0.0184,0.8948,0.4700,0.0087</t>
   </si>
   <si>
     <t>0.9512,0.0593,0.0091,0.0022</t>
   </si>
   <si>
-    <t>0.8989,0.1176,0.0129,0.0017</t>
-  </si>
-  <si>
-    <t>0.8633,0.0597,0.0243,0.0258</t>
+    <t>0.8990,0.1176,0.0129,0.0017</t>
+  </si>
+  <si>
+    <t>0.8634,0.0597,0.0243,0.0257</t>
   </si>
   <si>
     <t>0.9317,0.0771,0.0133,0.0028</t>
@@ -1099,13 +1105,13 @@
     <t>0.9330,0.0677,0.0108,0.0010</t>
   </si>
   <si>
-    <t>0.9276,0.0211,0.0161,0.0227</t>
+    <t>0.9277,0.0211,0.0161,0.0227</t>
   </si>
   <si>
     <t>0.9361,0.0602,0.0135,0.0011</t>
   </si>
   <si>
-    <t>0.4530,0.0667,0.1925,0.0108</t>
+    <t>0.4533,0.0667,0.1924,0.0108</t>
   </si>
   <si>
     <t>0.9682,0.0322,0.0083,0.0009</t>
@@ -1123,25 +1129,25 @@
     <t>0.9682,0.0223,0.0085,0.0029</t>
   </si>
   <si>
-    <t>0.9357,0.0177,0.0168,0.0167</t>
-  </si>
-  <si>
-    <t>0.9646,0.0283,0.0078,0.0033</t>
+    <t>0.9358,0.0177,0.0167,0.0167</t>
+  </si>
+  <si>
+    <t>0.9647,0.0283,0.0078,0.0033</t>
   </si>
   <si>
     <t>0.9701,0.0289,0.0076,0.0006</t>
   </si>
   <si>
-    <t>0.1259,0.0013,0.9212,0.0009</t>
-  </si>
-  <si>
-    <t>0.4578,0.0084,0.6245,0.0022</t>
-  </si>
-  <si>
-    <t>0.7330,0.0042,0.3532,0.0013</t>
-  </si>
-  <si>
-    <t>0.3745,0.0086,0.6898,0.0031</t>
+    <t>0.1260,0.0013,0.9212,0.0009</t>
+  </si>
+  <si>
+    <t>0.4580,0.0084,0.6244,0.0022</t>
+  </si>
+  <si>
+    <t>0.7332,0.0042,0.3530,0.0013</t>
+  </si>
+  <si>
+    <t>0.3745,0.0086,0.6897,0.0031</t>
   </si>
   <si>
     <t>0.0279,0.9693,0.0156,0.0007</t>
@@ -1150,7 +1156,7 @@
     <t>0.0099,0.9853,0.0151,0.0007</t>
   </si>
   <si>
-    <t>0.0787,0.9105,0.0676,0.0094</t>
+    <t>0.0788,0.9105,0.0676,0.0094</t>
   </si>
   <si>
     <t>0.0727,0.9292,0.0311,0.0026</t>
@@ -1159,25 +1165,25 @@
     <t>0.0194,0.9760,0.0167,0.0007</t>
   </si>
   <si>
-    <t>0.0025,0.9946,0.0081,0.0003</t>
-  </si>
-  <si>
-    <t>0.6162,0.3863,0.0406,0.0040</t>
-  </si>
-  <si>
-    <t>0.5550,0.1119,0.2934,0.0167</t>
-  </si>
-  <si>
-    <t>0.4106,0.0227,0.5618,0.0155</t>
-  </si>
-  <si>
-    <t>0.4968,0.0598,0.4532,0.0183</t>
-  </si>
-  <si>
-    <t>0.5428,0.0418,0.4342,0.0112</t>
-  </si>
-  <si>
-    <t>0.0249,0.1774,0.3350,0.5903</t>
+    <t>0.0026,0.9946,0.0081,0.0003</t>
+  </si>
+  <si>
+    <t>0.6164,0.3862,0.0405,0.0040</t>
+  </si>
+  <si>
+    <t>0.5552,0.1119,0.2932,0.0167</t>
+  </si>
+  <si>
+    <t>0.4106,0.0227,0.5617,0.0155</t>
+  </si>
+  <si>
+    <t>0.4970,0.0598,0.4530,0.0183</t>
+  </si>
+  <si>
+    <t>0.5429,0.0418,0.4341,0.0112</t>
+  </si>
+  <si>
+    <t>0.0249,0.1775,0.3351,0.5901</t>
   </si>
   <si>
     <t>0.0007,0.9967,0.0290,0.0008</t>
@@ -1186,25 +1192,25 @@
     <t>0.0007,0.9964,0.0229,0.0010</t>
   </si>
   <si>
-    <t>0.0230,0.9478,0.0521,0.0183</t>
+    <t>0.0230,0.9478,0.0521,0.0182</t>
   </si>
   <si>
     <t>0.0007,0.9950,0.0664,0.0017</t>
   </si>
   <si>
-    <t>0.0157,0.9717,0.0682,0.0038</t>
-  </si>
-  <si>
-    <t>0.4421,0.6062,0.0350,0.0044</t>
-  </si>
-  <si>
-    <t>0.3610,0.6768,0.0383,0.0045</t>
+    <t>0.0157,0.9716,0.0682,0.0038</t>
+  </si>
+  <si>
+    <t>0.4422,0.6062,0.0350,0.0044</t>
+  </si>
+  <si>
+    <t>0.3612,0.6767,0.0383,0.0045</t>
   </si>
   <si>
     <t>0.9507,0.0268,0.0142,0.0057</t>
   </si>
   <si>
-    <t>0.9398,0.0276,0.0120,0.0119</t>
+    <t>0.9399,0.0276,0.0120,0.0119</t>
   </si>
   <si>
     <t>0.9645,0.0204,0.0114,0.0024</t>
@@ -1213,10 +1219,10 @@
     <t>0.9557,0.0183,0.0229,0.0012</t>
   </si>
   <si>
-    <t>0.8640,0.0180,0.0315,0.0473</t>
-  </si>
-  <si>
-    <t>0.9264,0.0478,0.0225,0.0066</t>
+    <t>0.8641,0.0180,0.0314,0.0472</t>
+  </si>
+  <si>
+    <t>0.9265,0.0478,0.0225,0.0066</t>
   </si>
   <si>
     <t>0.9763,0.0162,0.0094,0.0005</t>
@@ -1225,31 +1231,31 @@
     <t>0.9758,0.0156,0.0095,0.0004</t>
   </si>
   <si>
-    <t>0.0325,0.4703,0.7471,0.0176</t>
-  </si>
-  <si>
-    <t>0.0266,0.5111,0.8774,0.0051</t>
-  </si>
-  <si>
-    <t>0.0122,0.1521,0.9390,0.0066</t>
-  </si>
-  <si>
-    <t>0.1402,0.0187,0.8866,0.0038</t>
-  </si>
-  <si>
-    <t>0.8098,0.0087,0.2018,0.0019</t>
-  </si>
-  <si>
-    <t>0.5985,0.1158,0.2394,0.0128</t>
-  </si>
-  <si>
-    <t>0.4556,0.0077,0.4366,0.0220</t>
-  </si>
-  <si>
-    <t>0.5141,0.0652,0.4188,0.0218</t>
-  </si>
-  <si>
-    <t>0.5732,0.0048,0.0114,0.3437</t>
+    <t>0.0325,0.4704,0.7471,0.0176</t>
+  </si>
+  <si>
+    <t>0.0266,0.5113,0.8773,0.0051</t>
+  </si>
+  <si>
+    <t>0.0122,0.1523,0.9390,0.0066</t>
+  </si>
+  <si>
+    <t>0.1403,0.0187,0.8865,0.0038</t>
+  </si>
+  <si>
+    <t>0.8099,0.0087,0.2017,0.0019</t>
+  </si>
+  <si>
+    <t>0.5987,0.1157,0.2392,0.0128</t>
+  </si>
+  <si>
+    <t>0.4558,0.0077,0.4365,0.0220</t>
+  </si>
+  <si>
+    <t>0.5143,0.0652,0.4187,0.0218</t>
+  </si>
+  <si>
+    <t>0.5735,0.0048,0.0114,0.3434</t>
   </si>
   <si>
     <t>0.0084,0.0170,0.0045,0.9971</t>
@@ -1258,7 +1264,7 @@
     <t>0.0236,0.0097,0.0042,0.9918</t>
   </si>
   <si>
-    <t>0.1383,0.0080,0.0148,0.8949</t>
+    <t>0.1384,0.0080,0.0148,0.8948</t>
   </si>
   <si>
     <t>0.0091,0.9146,0.5826,0.0100</t>
@@ -1267,64 +1273,64 @@
     <t>0.9695,0.0198,0.0129,0.0005</t>
   </si>
   <si>
-    <t>0.3903,0.6294,0.0322,0.0053</t>
+    <t>0.3904,0.6294,0.0322,0.0053</t>
   </si>
   <si>
     <t>0.9686,0.0150,0.0154,0.0005</t>
   </si>
   <si>
-    <t>0.5902,0.4607,0.0199,0.0023</t>
-  </si>
-  <si>
-    <t>0.9304,0.0203,0.0193,0.0091</t>
+    <t>0.5903,0.4606,0.0199,0.0023</t>
+  </si>
+  <si>
+    <t>0.9304,0.0203,0.0192,0.0091</t>
   </si>
   <si>
     <t>0.0953,0.0018,0.8626,0.0007</t>
   </si>
   <si>
-    <t>0.3753,0.0032,0.4957,0.0031</t>
+    <t>0.3756,0.0032,0.4955,0.0031</t>
   </si>
   <si>
     <t>0.0007,0.0138,0.9558,0.0001</t>
   </si>
   <si>
-    <t>0.9294,0.0048,0.0309,0.0043</t>
+    <t>0.9295,0.0048,0.0309,0.0043</t>
   </si>
   <si>
     <t>0.8966,0.0600,0.0204,0.0113</t>
   </si>
   <si>
-    <t>0.7258,0.1752,0.0711,0.0049</t>
+    <t>0.7260,0.1752,0.0711,0.0049</t>
   </si>
   <si>
     <t>0.8536,0.0390,0.0870,0.0049</t>
   </si>
   <si>
-    <t>0.7992,0.0713,0.1151,0.0073</t>
-  </si>
-  <si>
-    <t>0.4023,0.4504,0.1482,0.0411</t>
-  </si>
-  <si>
-    <t>0.7860,0.0693,0.1299,0.0058</t>
-  </si>
-  <si>
-    <t>0.6686,0.0494,0.1894,0.0390</t>
-  </si>
-  <si>
-    <t>0.9571,0.0377,0.0138,0.0013</t>
-  </si>
-  <si>
-    <t>0.8867,0.0169,0.0094,0.0443</t>
+    <t>0.7993,0.0713,0.1151,0.0073</t>
+  </si>
+  <si>
+    <t>0.4024,0.4504,0.1481,0.0411</t>
+  </si>
+  <si>
+    <t>0.7860,0.0692,0.1299,0.0058</t>
+  </si>
+  <si>
+    <t>0.6687,0.0494,0.1893,0.0390</t>
+  </si>
+  <si>
+    <t>0.9572,0.0377,0.0138,0.0013</t>
+  </si>
+  <si>
+    <t>0.8868,0.0169,0.0094,0.0442</t>
   </si>
   <si>
     <t>0.9491,0.0290,0.0190,0.0009</t>
   </si>
   <si>
-    <t>0.9595,0.0314,0.0114,0.0008</t>
-  </si>
-  <si>
-    <t>0.9549,0.0334,0.0159,0.0008</t>
+    <t>0.9596,0.0314,0.0114,0.0008</t>
+  </si>
+  <si>
+    <t>0.9549,0.0334,0.0158,0.0008</t>
   </si>
   <si>
     <t>0.9523,0.0313,0.0188,0.0016</t>
@@ -1336,46 +1342,46 @@
     <t>0.9644,0.0309,0.0093,0.0006</t>
   </si>
   <si>
-    <t>0.2613,0.7079,0.1021,0.0278</t>
-  </si>
-  <si>
-    <t>0.4212,0.6185,0.0400,0.0054</t>
-  </si>
-  <si>
-    <t>0.8853,0.1078,0.0217,0.0014</t>
-  </si>
-  <si>
-    <t>0.7828,0.1932,0.0403,0.0052</t>
+    <t>0.2614,0.7079,0.1020,0.0278</t>
+  </si>
+  <si>
+    <t>0.4213,0.6184,0.0400,0.0054</t>
+  </si>
+  <si>
+    <t>0.8853,0.1078,0.0216,0.0014</t>
+  </si>
+  <si>
+    <t>0.7829,0.1931,0.0402,0.0052</t>
   </si>
   <si>
     <t>0.9492,0.0477,0.0118,0.0009</t>
   </si>
   <si>
-    <t>0.7791,0.2098,0.0315,0.0031</t>
+    <t>0.7792,0.2097,0.0315,0.0031</t>
   </si>
   <si>
     <t>0.9462,0.0386,0.0157,0.0008</t>
   </si>
   <si>
-    <t>0.8938,0.0764,0.0298,0.0022</t>
-  </si>
-  <si>
-    <t>0.3663,0.3522,0.1980,0.0090</t>
+    <t>0.8939,0.0764,0.0298,0.0022</t>
+  </si>
+  <si>
+    <t>0.3664,0.3522,0.1980,0.0090</t>
   </si>
   <si>
     <t>0.8207,0.1621,0.0285,0.0020</t>
   </si>
   <si>
-    <t>0.1020,0.0082,0.9079,0.0051</t>
-  </si>
-  <si>
-    <t>0.0505,0.0959,0.7356,0.0708</t>
-  </si>
-  <si>
-    <t>0.3306,0.0165,0.6833,0.0072</t>
-  </si>
-  <si>
-    <t>0.0700,0.3090,0.6099,0.0390</t>
+    <t>0.1021,0.0082,0.9079,0.0051</t>
+  </si>
+  <si>
+    <t>0.0506,0.0959,0.7357,0.0707</t>
+  </si>
+  <si>
+    <t>0.3309,0.0165,0.6831,0.0072</t>
+  </si>
+  <si>
+    <t>0.0700,0.3090,0.6098,0.0390</t>
   </si>
   <si>
     <t>0.1792,0.0371,0.8160,0.0104</t>
@@ -1384,34 +1390,34 @@
     <t>0.1972,0.0010,0.8884,0.0005</t>
   </si>
   <si>
-    <t>0.2435,0.0040,0.8143,0.0022</t>
-  </si>
-  <si>
-    <t>0.3145,0.0543,0.6206,0.0291</t>
-  </si>
-  <si>
-    <t>0.5090,0.0213,0.4549,0.0138</t>
-  </si>
-  <si>
-    <t>0.4345,0.1234,0.4241,0.0322</t>
-  </si>
-  <si>
-    <t>0.4050,0.0504,0.5736,0.0120</t>
-  </si>
-  <si>
-    <t>0.4052,0.1038,0.4938,0.0132</t>
-  </si>
-  <si>
-    <t>0.4054,0.0366,0.5450,0.0213</t>
-  </si>
-  <si>
-    <t>0.4973,0.0457,0.4749,0.0150</t>
-  </si>
-  <si>
-    <t>0.4478,0.0530,0.5014,0.0233</t>
-  </si>
-  <si>
-    <t>0.2872,0.5640,0.1019,0.0321</t>
+    <t>0.2436,0.0040,0.8142,0.0022</t>
+  </si>
+  <si>
+    <t>0.3147,0.0543,0.6205,0.0291</t>
+  </si>
+  <si>
+    <t>0.5091,0.0213,0.4547,0.0138</t>
+  </si>
+  <si>
+    <t>0.4346,0.1234,0.4239,0.0322</t>
+  </si>
+  <si>
+    <t>0.4051,0.0504,0.5735,0.0120</t>
+  </si>
+  <si>
+    <t>0.4052,0.1038,0.4937,0.0132</t>
+  </si>
+  <si>
+    <t>0.4054,0.0366,0.5449,0.0213</t>
+  </si>
+  <si>
+    <t>0.4974,0.0458,0.4748,0.0150</t>
+  </si>
+  <si>
+    <t>0.4479,0.0530,0.5013,0.0233</t>
+  </si>
+  <si>
+    <t>0.2873,0.5639,0.1018,0.0321</t>
   </si>
   <si>
     <t>0.3040,0.7481,0.0203,0.0021</t>
@@ -1426,52 +1432,52 @@
     <t>0.8590,0.1584,0.0138,0.0016</t>
   </si>
   <si>
-    <t>0.4584,0.2485,0.2488,0.0204</t>
-  </si>
-  <si>
-    <t>0.8255,0.0095,0.1612,0.0028</t>
-  </si>
-  <si>
-    <t>0.4427,0.0376,0.4860,0.0327</t>
-  </si>
-  <si>
-    <t>0.3691,0.0178,0.5460,0.0283</t>
-  </si>
-  <si>
-    <t>0.7332,0.0151,0.2547,0.0040</t>
-  </si>
-  <si>
-    <t>0.3144,0.0266,0.6526,0.0211</t>
-  </si>
-  <si>
-    <t>0.1031,0.0747,0.8371,0.0288</t>
-  </si>
-  <si>
-    <t>0.1824,0.0401,0.7947,0.0196</t>
-  </si>
-  <si>
-    <t>0.0571,0.0702,0.9131,0.0085</t>
-  </si>
-  <si>
-    <t>0.1597,0.0194,0.8662,0.0047</t>
-  </si>
-  <si>
-    <t>0.9613,0.0415,0.0074,0.0006</t>
+    <t>0.4585,0.2485,0.2487,0.0204</t>
+  </si>
+  <si>
+    <t>0.8256,0.0095,0.1610,0.0028</t>
+  </si>
+  <si>
+    <t>0.4428,0.0376,0.4859,0.0327</t>
+  </si>
+  <si>
+    <t>0.3692,0.0178,0.5459,0.0283</t>
+  </si>
+  <si>
+    <t>0.7334,0.0151,0.2545,0.0040</t>
+  </si>
+  <si>
+    <t>0.3145,0.0266,0.6526,0.0210</t>
+  </si>
+  <si>
+    <t>0.1031,0.0747,0.8370,0.0288</t>
+  </si>
+  <si>
+    <t>0.1825,0.0401,0.7946,0.0196</t>
+  </si>
+  <si>
+    <t>0.0571,0.0702,0.9130,0.0085</t>
+  </si>
+  <si>
+    <t>0.1598,0.0194,0.8662,0.0047</t>
+  </si>
+  <si>
+    <t>0.9614,0.0415,0.0074,0.0006</t>
   </si>
   <si>
     <t>0.9417,0.0624,0.0119,0.0010</t>
   </si>
   <si>
-    <t>0.8942,0.1338,0.0165,0.0036</t>
-  </si>
-  <si>
-    <t>0.9386,0.0347,0.0128,0.0109</t>
-  </si>
-  <si>
-    <t>0.9315,0.0828,0.0136,0.0018</t>
-  </si>
-  <si>
-    <t>0.9354,0.0766,0.0113,0.0016</t>
+    <t>0.8942,0.1337,0.0165,0.0036</t>
+  </si>
+  <si>
+    <t>0.9386,0.0347,0.0127,0.0109</t>
+  </si>
+  <si>
+    <t>0.9316,0.0828,0.0136,0.0018</t>
+  </si>
+  <si>
+    <t>0.9355,0.0765,0.0113,0.0016</t>
   </si>
   <si>
     <t>0.9331,0.0812,0.0118,0.0017</t>
@@ -1480,28 +1486,28 @@
     <t>0.9556,0.0473,0.0083,0.0009</t>
   </si>
   <si>
-    <t>0.6270,0.0269,0.3522,0.0031</t>
+    <t>0.6273,0.0269,0.3520,0.0031</t>
   </si>
   <si>
     <t>0.5967,0.0957,0.2398,0.0062</t>
   </si>
   <si>
-    <t>0.6644,0.0492,0.2129,0.0178</t>
-  </si>
-  <si>
-    <t>0.0500,0.0149,0.9486,0.0044</t>
+    <t>0.6646,0.0492,0.2128,0.0178</t>
+  </si>
+  <si>
+    <t>0.0501,0.0149,0.9485,0.0044</t>
   </si>
   <si>
     <t>0.0233,0.0087,0.9673,0.0055</t>
   </si>
   <si>
-    <t>0.1998,0.0300,0.7874,0.0122</t>
+    <t>0.1998,0.0300,0.7873,0.0122</t>
   </si>
   <si>
     <t>0.0093,0.0037,0.9854,0.0016</t>
   </si>
   <si>
-    <t>0.2465,0.0216,0.7708,0.0082</t>
+    <t>0.2466,0.0216,0.7707,0.0082</t>
   </si>
   <si>
     <t>0.0031,0.0006,0.9969,0.0001</t>
@@ -1510,73 +1516,73 @@
     <t>0.0800,0.0161,0.9110,0.0088</t>
   </si>
   <si>
-    <t>0.3527,0.0657,0.5798,0.0223</t>
-  </si>
-  <si>
-    <t>0.5107,0.0094,0.4445,0.0119</t>
-  </si>
-  <si>
-    <t>0.6156,0.0056,0.3080,0.0111</t>
-  </si>
-  <si>
-    <t>0.7920,0.0103,0.2066,0.0028</t>
+    <t>0.3528,0.0657,0.5796,0.0223</t>
+  </si>
+  <si>
+    <t>0.5109,0.0094,0.4443,0.0119</t>
+  </si>
+  <si>
+    <t>0.6157,0.0056,0.3079,0.0110</t>
+  </si>
+  <si>
+    <t>0.7922,0.0103,0.2064,0.0028</t>
   </si>
   <si>
     <t>0.9424,0.0637,0.0082,0.0010</t>
   </si>
   <si>
-    <t>0.9127,0.0476,0.0152,0.0161</t>
+    <t>0.9128,0.0476,0.0152,0.0161</t>
   </si>
   <si>
     <t>0.9292,0.0858,0.0095,0.0011</t>
   </si>
   <si>
-    <t>0.8222,0.1985,0.0193,0.0026</t>
+    <t>0.8223,0.1984,0.0193,0.0026</t>
   </si>
   <si>
     <t>0.9572,0.0409,0.0092,0.0011</t>
   </si>
   <si>
-    <t>0.8634,0.1705,0.0141,0.0021</t>
-  </si>
-  <si>
-    <t>0.9374,0.0588,0.0151,0.0032</t>
+    <t>0.8635,0.1704,0.0141,0.0021</t>
+  </si>
+  <si>
+    <t>0.9375,0.0588,0.0151,0.0032</t>
   </si>
   <si>
     <t>0.9196,0.0856,0.0151,0.0029</t>
   </si>
   <si>
-    <t>0.1964,0.1155,0.7104,0.0193</t>
+    <t>0.1965,0.1156,0.7104,0.0193</t>
   </si>
   <si>
     <t>0.1226,0.0192,0.8928,0.0048</t>
   </si>
   <si>
-    <t>0.0579,0.0050,0.9502,0.0021</t>
-  </si>
-  <si>
-    <t>0.2733,0.0160,0.7576,0.0064</t>
-  </si>
-  <si>
-    <t>0.2816,0.0026,0.8167,0.0011</t>
-  </si>
-  <si>
-    <t>0.2460,0.0754,0.2097,0.4134</t>
-  </si>
-  <si>
-    <t>0.3104,0.0444,0.6194,0.0277</t>
-  </si>
-  <si>
-    <t>0.0242,0.0389,0.9377,0.0098</t>
-  </si>
-  <si>
-    <t>0.7321,0.0073,0.0266,0.1112</t>
-  </si>
-  <si>
-    <t>0.0793,0.0274,0.0132,0.9478</t>
-  </si>
-  <si>
-    <t>0.0593,0.0101,0.0131,0.9713</t>
+    <t>0.0580,0.0050,0.9502,0.0021</t>
+  </si>
+  <si>
+    <t>0.2734,0.0160,0.7576,0.0064</t>
+  </si>
+  <si>
+    <t>0.2817,0.0026,0.8167,0.0011</t>
+  </si>
+  <si>
+    <t>0.2462,0.0754,0.2097,0.4131</t>
+  </si>
+  <si>
+    <t>0.3106,0.0445,0.6193,0.0277</t>
+  </si>
+  <si>
+    <t>0.0242,0.0390,0.9377,0.0098</t>
+  </si>
+  <si>
+    <t>0.7324,0.0073,0.0266,0.1110</t>
+  </si>
+  <si>
+    <t>0.0794,0.0274,0.0132,0.9478</t>
+  </si>
+  <si>
+    <t>0.0593,0.0101,0.0131,0.9712</t>
   </si>
   <si>
     <t>0.0025,0.0014,0.0072,0.9993</t>
@@ -1585,7 +1591,7 @@
     <t>0.0095,0.0070,0.0059,0.9971</t>
   </si>
   <si>
-    <t>0.4636,0.0303,0.0671,0.3550</t>
+    <t>0.4638,0.0303,0.0671,0.3547</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,10 +2002,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,10 +2016,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,10 +2030,10 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,10 +2044,10 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,10 +2058,10 @@
         <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,10 +2072,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,10 +2086,10 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,10 +2100,10 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,10 +2114,10 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,10 +2128,10 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2136,10 +2142,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,10 +2156,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,10 +2170,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,10 +2184,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,10 +2198,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,10 +2212,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,10 +2226,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,10 +2240,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,10 +2254,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,10 +2268,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,10 +2282,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,10 +2296,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,10 +2310,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,10 +2324,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,10 +2338,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,10 +2352,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,10 +2366,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2374,10 +2380,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,10 +2394,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,10 +2408,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,10 +2422,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2430,10 +2436,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2444,10 +2450,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,10 +2464,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,10 +2478,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2492,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,10 +2506,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,10 +2520,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,10 +2534,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2548,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,10 +2562,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,10 +2576,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2593,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,10 +2604,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,10 +2618,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,10 +2632,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,10 +2646,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,10 +2660,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,10 +2674,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,10 +2688,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,10 +2702,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,10 +2716,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,10 +2730,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2738,10 +2744,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,10 +2758,10 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,10 +2772,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,10 +2786,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2794,10 +2800,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,10 +2814,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2828,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,10 +2842,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,10 +2856,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2870,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,10 +2884,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,10 +2898,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,10 +2912,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,10 +2926,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,10 +2940,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2957,7 @@
         <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2968,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2982,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2996,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3010,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3108,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3122,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3136,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3150,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3164,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3178,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,10 +3192,10 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,10 +3206,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,10 +3220,10 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,10 +3234,10 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,10 +3248,10 @@
         <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,10 +3262,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,10 +3276,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,10 +3304,10 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,10 +3318,10 @@
         <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,10 +3332,10 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,10 +3346,10 @@
         <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,10 +3360,10 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,10 +3374,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,10 +3388,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,10 +3402,10 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,10 +3416,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,10 +3430,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,10 +3444,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,10 +3458,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,10 +3472,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,10 +3486,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,10 +3500,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3514,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,10 +3528,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,10 +3542,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,10 +3556,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,10 +3570,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,10 +3584,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3601,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,10 +3612,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,7 +3629,7 @@
         <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,10 +3640,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,10 +3654,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,10 +3668,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,10 +3682,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,10 +3696,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3710,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,10 +3724,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,10 +3738,10 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,10 +3752,10 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,10 +3766,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,10 +3780,10 @@
         <v>259</v>
       </c>
       <c r="C131" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,10 +3794,10 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,10 +3808,10 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3816,10 +3822,10 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,10 +3836,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3850,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3864,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,10 +3878,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,10 +3892,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,10 +3906,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3920,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3937,7 @@
         <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3942,10 +3948,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,10 +3962,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4018,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4026,10 +4032,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,10 +4046,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,10 +4060,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,10 +4074,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,10 +4088,10 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,10 +4102,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4113,7 +4119,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,10 +4130,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,10 +4144,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,10 +4158,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,10 +4172,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,10 +4186,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,10 +4200,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,7 +4217,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,10 +4228,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,10 +4242,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,10 +4256,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,10 +4270,10 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,10 +4284,10 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,10 +4298,10 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,10 +4312,10 @@
         <v>259</v>
       </c>
       <c r="C169" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,10 +4326,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,10 +4340,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,10 +4354,10 @@
         <v>259</v>
       </c>
       <c r="C172" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,10 +4368,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,10 +4382,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,10 +4396,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,10 +4410,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,10 +4424,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,10 +4438,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,10 +4452,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4460,10 +4466,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4483,7 @@
         <v>264</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,10 +4494,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,10 +4508,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,10 +4522,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,10 +4536,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4550,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,10 +4564,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,10 +4578,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,10 +4592,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,10 +4606,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,10 +4620,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,10 +4648,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4665,7 @@
         <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,10 +4676,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4693,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,10 +4704,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,10 +4718,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,10 +4732,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,10 +4746,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,10 +4760,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,10 +4774,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4791,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,10 +4802,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4819,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,10 +4830,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,10 +4844,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,10 +4858,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,10 +4872,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,10 +4886,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,10 +4900,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,10 +4914,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,10 +4928,10 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,10 +4942,10 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,10 +4956,10 @@
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,10 +4970,10 @@
         <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4978,10 +4984,10 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4992,10 +4998,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,10 +5012,10 @@
         <v>259</v>
       </c>
       <c r="C219" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,10 +5026,10 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,10 +5040,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,10 +5054,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,10 +5068,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,10 +5082,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,10 +5096,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,10 +5110,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,10 +5124,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,10 +5138,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,10 +5152,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,10 +5166,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,10 +5180,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,10 +5194,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,10 +5208,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,10 +5222,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,10 +5236,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,10 +5250,10 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,10 +5264,10 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,10 +5278,10 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,10 +5292,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,10 +5306,10 @@
         <v>259</v>
       </c>
       <c r="C240" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,10 +5320,10 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,10 +5334,10 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,10 +5348,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,10 +5362,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,10 +5376,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,10 +5390,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,10 +5404,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5421,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,10 +5432,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,10 +5446,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,10 +5460,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
